--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486796_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486796_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4337</v>
+        <v>1.9497</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7784</v>
+        <v>-0.0351</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6553</v>
+        <v>1.9848</v>
       </c>
       <c r="G2" t="n">
         <v>2.7911</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2565</v>
+        <v>0.7725</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5439</v>
+        <v>0.7304</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7126</v>
+        <v>0.0421</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2277</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>K. RODRIGUEZ AGUILERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.375</v>
+        <v>1.7751</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3733</v>
+        <v>0.131</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0017</v>
+        <v>1.6441</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1286</v>
+        <v>3.4052</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3725</v>
+        <v>-0.5374</v>
       </c>
       <c r="I3" t="n">
-        <v>1.501</v>
+        <v>3.9426</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3712</v>
+        <v>2.9931</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2491</v>
+        <v>1.1189</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1221</v>
+        <v>1.8741</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7574</v>
+        <v>0.4121</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-1.6563</v>
       </c>
       <c r="O3" t="n">
-        <v>1.379</v>
+        <v>2.0684</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1585</v>
+        <v>-3.0892</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5446</v>
+        <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8603</v>
+        <v>-1.186</v>
       </c>
       <c r="T3" t="n">
-        <v>1.875</v>
+        <v>-0.3866</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0147</v>
+        <v>-0.7994</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2856</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. RODRIGUEZ AGUILERA</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5835</v>
+        <v>1.1079</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8619</v>
+        <v>-0.0677</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4454</v>
+        <v>1.1756</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4052</v>
+        <v>1.1286</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5374</v>
+        <v>-0.3725</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9426</v>
+        <v>1.501</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9931</v>
+        <v>0.3712</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1189</v>
+        <v>0.2491</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8741</v>
+        <v>0.1221</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4121</v>
+        <v>0.7574</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6563</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.0684</v>
+        <v>1.379</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0892</v>
+        <v>-1.1585</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3776</v>
+        <v>-0.4068</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3796</v>
+        <v>0.434</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.998</v>
+        <v>-0.8409</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6138</v>
+        <v>0.2856</v>
       </c>
       <c r="X4" t="n">
         <v>-0.2856</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1888</v>
+        <v>0.5187</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.7839</v>
+        <v>-2.1012</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5951</v>
+        <v>2.6199</v>
       </c>
       <c r="G5" t="n">
         <v>0.743</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8659</v>
+        <v>-0.1584</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6622</v>
+        <v>0.0205</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2037</v>
+        <v>-0.1789</v>
       </c>
       <c r="V5" t="n">
         <v>0.8995</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4916</v>
+        <v>0.4531</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1459</v>
+        <v>-1.5736</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6543</v>
+        <v>2.0267</v>
       </c>
       <c r="G6" t="n">
         <v>0.2433</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2136</v>
+        <v>-0.2688</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5518</v>
+        <v>0.0205</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.2893</v>
       </c>
       <c r="V6" t="n">
         <v>0.2856</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. JOAO</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8128</v>
+        <v>-0.4506</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7903</v>
+        <v>-1.8908</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9775</v>
+        <v>1.4403</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9646</v>
+        <v>1.0942</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0414</v>
+        <v>-0.504</v>
       </c>
       <c r="I7" t="n">
-        <v>1.006</v>
+        <v>1.5982</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3444</v>
+        <v>0.1989</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3037</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>-0.6081</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6201</v>
+        <v>0.8953</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3451</v>
+        <v>-1.311</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9653</v>
+        <v>2.2063</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9308</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0892</v>
+        <v>-2.3169</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1322</v>
+        <v>-0.1586</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3311</v>
+        <v>0.2272</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1989</v>
+        <v>-0.3858</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2856</v>
+        <v>-0.6138</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>A. JOAO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0521</v>
+        <v>-0.8046</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5229</v>
+        <v>-2.5834</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4708</v>
+        <v>1.7788</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2191</v>
+        <v>0.9646</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.724</v>
+        <v>-0.0414</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5048</v>
+        <v>1.006</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9769</v>
+        <v>0.3444</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.2406</v>
+        <v>0.3037</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2637</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7577</v>
+        <v>0.6201</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4833</v>
+        <v>-0.3451</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2411</v>
+        <v>0.9653</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8962</v>
+        <v>-3.0892</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9308</v>
+        <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7889</v>
+        <v>-0.124</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5512</v>
+        <v>-0.1242</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2377</v>
+        <v>0.0002</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7989</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3237</v>
+        <v>-1.7513</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3667</v>
+        <v>-1.8745</v>
       </c>
       <c r="F9" t="n">
-        <v>1.043</v>
+        <v>0.1232</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0942</v>
+        <v>-0.2191</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.504</v>
+        <v>-2.724</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5982</v>
+        <v>2.5048</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1989</v>
+        <v>-0.9769</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8070000000000001</v>
+        <v>-2.2406</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6081</v>
+        <v>1.2637</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8953</v>
+        <v>0.7577</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.311</v>
+        <v>-0.4833</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2063</v>
+        <v>1.2411</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7723</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3169</v>
+        <v>-2.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0317</v>
+        <v>0.0897</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2486</v>
+        <v>0.1997</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7831</v>
+        <v>-0.1099</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6138</v>
+        <v>-0.6565</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7989</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6138</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.8723</v>
+        <v>-5.0435</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8269</v>
+        <v>-4.0478</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0454</v>
+        <v>-0.9957</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7041</v>
@@ -1234,13 +1234,13 @@
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7667</v>
+        <v>0.0621</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6622</v>
+        <v>0.117</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1045</v>
+        <v>-0.0549</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8568</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3491</v>
+        <v>-2.2455</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.1468</v>
+        <v>-14.0431</v>
       </c>
       <c r="F11" t="n">
         <v>11.7977</v>
@@ -1288,10 +1288,10 @@
         <v>0.5605000000000002</v>
       </c>
       <c r="K11" t="n">
-        <v>1.385199999999999</v>
+        <v>1.3852</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8248999999999997</v>
+        <v>-0.8248999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>6.8861</v>
@@ -1303,7 +1303,7 @@
         <v>15.1686</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.7577</v>
+        <v>-6.757700000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-21.2385</v>
@@ -1312,13 +1312,13 @@
         <v>14.4807</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.482</v>
+        <v>-1.3783</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1345999999999999</v>
+        <v>1.2385</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.6166</v>
+        <v>-2.6168</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5559</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.8149</v>
+        <v>7.0206</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9387</v>
+        <v>4.3182</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8762</v>
+        <v>2.7024</v>
       </c>
       <c r="G12" t="n">
         <v>4.0623</v>
@@ -1390,13 +1390,13 @@
         <v>3.0892</v>
       </c>
       <c r="S12" t="n">
-        <v>1.208</v>
+        <v>0.4137</v>
       </c>
       <c r="T12" t="n">
-        <v>1.02</v>
+        <v>0.3994</v>
       </c>
       <c r="U12" t="n">
-        <v>0.188</v>
+        <v>0.0142</v>
       </c>
       <c r="V12" t="n">
         <v>0.6138</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6233</v>
+        <v>4.7516</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8608</v>
+        <v>3.8856</v>
       </c>
       <c r="G13" t="n">
         <v>2.152</v>
@@ -1468,13 +1468,13 @@
         <v>3.2823</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3475</v>
+        <v>0.4758</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3857</v>
+        <v>0.4891</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0382</v>
+        <v>-0.0133</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9566</v>
+        <v>2.2132</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4961</v>
+        <v>-0.2893</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4528</v>
+        <v>2.5025</v>
       </c>
       <c r="G14" t="n">
         <v>0.3789</v>
@@ -1546,13 +1546,13 @@
         <v>2.3169</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7392</v>
+        <v>-0.4827</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2486</v>
+        <v>-0.0418</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4906</v>
+        <v>-0.4409</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. DEUS VERA</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3722</v>
+        <v>1.21</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3617</v>
+        <v>-0.1858</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0105</v>
+        <v>1.3958</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0828</v>
+        <v>-3.0757</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2275</v>
+        <v>1.4478</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1447</v>
+        <v>-4.5235</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0488</v>
+        <v>-1.7225</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0488</v>
+        <v>2.4144</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-4.1369</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1316</v>
+        <v>-1.3531</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2763</v>
+        <v>-0.9665</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1447</v>
+        <v>-0.3866</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1585</v>
+        <v>3.2823</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.2277</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9927</v>
+        <v>0.0201</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0164</v>
+        <v>-0.2478</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2856</v>
+        <v>3.3548</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2856</v>
+        <v>3.6404</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. SECK DIOP</t>
+          <t>R. DEUS VERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8206</v>
+        <v>1.1613</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8268</v>
+        <v>0.0514</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6474</v>
+        <v>1.1098</v>
       </c>
       <c r="G16" t="n">
-        <v>0.531</v>
+        <v>-0.0828</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1654</v>
+        <v>-0.2275</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6345</v>
+        <v>0.1447</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0406</v>
+        <v>0.0488</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3384</v>
+        <v>0.0488</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.379</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5716</v>
+        <v>-0.1316</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.2763</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2555</v>
+        <v>0.1447</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9308</v>
+        <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0386</v>
+        <v>0.7654</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.6824</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0445</v>
+        <v>0.083</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3282</v>
+        <v>0.2856</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. JENKINS BAFFOUR</t>
+          <t>K. SECK DIOP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1394</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.793</v>
+        <v>-0.8268</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6536</v>
+        <v>1.5481</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5034</v>
+        <v>0.531</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0482</v>
+        <v>2.1654</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5516</v>
+        <v>-1.6345</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2963</v>
+        <v>-0.0406</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3932</v>
+        <v>1.3384</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6895</v>
+        <v>-1.379</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2071</v>
+        <v>0.5716</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.345</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1379</v>
+        <v>-0.2555</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5571</v>
+        <v>-0.1379</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4688</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.0548</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>A. JENKINS BAFFOUR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3332</v>
+        <v>-0.6276</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5303</v>
+        <v>-1.2067</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1971</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0757</v>
+        <v>-0.5034</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4478</v>
+        <v>0.0482</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.5235</v>
+        <v>-0.5516</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7225</v>
+        <v>-0.2963</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4144</v>
+        <v>0.3932</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.1369</v>
+        <v>-0.6895</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3531</v>
+        <v>-0.2071</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9665</v>
+        <v>-0.345</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3866</v>
+        <v>0.1379</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2823</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7708</v>
+        <v>0.0689</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3244</v>
+        <v>0.0551</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4464</v>
+        <v>0.0139</v>
       </c>
       <c r="V18" t="n">
-        <v>3.3548</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.6404</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5986</v>
+        <v>-0.6483</v>
       </c>
       <c r="E19" t="n">
         <v>-0.8895</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2909</v>
+        <v>0.2412</v>
       </c>
       <c r="G19" t="n">
         <v>-0.731</v>
@@ -1936,13 +1936,13 @@
         <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0606</v>
+        <v>-0.1103</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1601</v>
+        <v>0.1104</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7895</v>
+        <v>-1.4752</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7573</v>
+        <v>-3.3436</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9678</v>
+        <v>1.8684</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5233</v>
@@ -2014,13 +2014,13 @@
         <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9268</v>
+        <v>1.2412</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3032</v>
+        <v>0.7169</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6236</v>
+        <v>0.5243</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0264</v>
+        <v>-4.8827</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6034</v>
+        <v>-3.5342</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.423</v>
+        <v>-1.3485</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4479</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4562</v>
+        <v>0.5999</v>
       </c>
       <c r="T21" t="n">
-        <v>1.627</v>
+        <v>0.6962</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1708</v>
+        <v>-0.0963</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4554</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3516</v>
+        <v>-6.0951</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.9643</v>
+        <v>-6.7575</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6127</v>
+        <v>0.6624</v>
       </c>
       <c r="G22" t="n">
         <v>-5.2066</v>
@@ -2170,13 +2170,13 @@
         <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3807</v>
+        <v>-0.1242</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3038</v>
+        <v>-0.097</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0769</v>
+        <v>-0.0272</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5712</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.348899999999998</v>
+        <v>3.349099999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.7977</v>
+        <v>-11.7978</v>
       </c>
       <c r="F23" t="n">
         <v>15.1468</v>
@@ -2221,7 +2221,7 @@
         <v>-14.3437</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.8862</v>
+        <v>-6.886200000000001</v>
       </c>
       <c r="K23" t="n">
         <v>8.282499999999999</v>
@@ -2236,7 +2236,7 @@
         <v>-1.3852</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8247000000000002</v>
+        <v>0.8247</v>
       </c>
       <c r="P23" t="n">
         <v>6.7578</v>
@@ -2248,19 +2248,19 @@
         <v>21.2385</v>
       </c>
       <c r="S23" t="n">
-        <v>2.482</v>
+        <v>2.4821</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6168</v>
+        <v>2.6166</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1346999999999999</v>
+        <v>-0.1345</v>
       </c>
       <c r="V23" t="n">
         <v>1.5558</v>
       </c>
       <c r="W23" t="n">
-        <v>6.952599999999999</v>
+        <v>6.9526</v>
       </c>
       <c r="X23" t="n">
         <v>-5.3967</v>
